--- a/rules/CORE-000158/negative/01/data/unit-test-coreid-CG0163-negative-1.xlsx
+++ b/rules/CORE-000158/negative/01/data/unit-test-coreid-CG0163-negative-1.xlsx
@@ -803,7 +803,7 @@
         <v>CO</v>
       </c>
       <c r="C5" s="4" t="str">
-        <v/>
+        <v>DM</v>
       </c>
       <c r="D5" s="4" t="str">
         <v>AB-99</v>
